--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1102-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1102-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E13F372E-7524-43E3-9A8A-D78EA0045B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DAB275D-D1B5-44AC-B570-2970A7926C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D2C28DED-442D-4304-868F-200F728AF785}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{FAF151BD-ADCE-4875-B591-866B15A11F32}"/>
   </bookViews>
   <sheets>
     <sheet name="1102-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1484,25 +1484,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE7DA32-4580-4D25-A442-E289B1EBF555}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81FABFA9-2652-4D76-AD5F-2E01F17625AD}">
   <dimension ref="A1:R69"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1656,7 +1656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2025</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2024</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2023</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2022</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2021</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2020</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2019</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2018</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2017</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2016</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2015</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2014</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2013</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>2012</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>2011</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>2010</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>2009</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>2008</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>2007</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>2006</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>2005</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>2004</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>2003</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>2002</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="40">
         <v>2001</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>2000</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="40">
         <v>1999</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="38">
         <v>1998</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="40">
         <v>1997</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="38">
         <v>1996</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="40">
         <v>1995</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="38">
         <v>1994</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>5.65</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="40">
         <v>1993</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="38">
         <v>1992</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="40">
         <v>1991</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="38">
         <v>1990</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="40">
         <v>1989</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="38">
         <v>1988</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="40">
         <v>1987</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="38">
         <v>1986</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="40">
         <v>1985</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="38">
         <v>1984</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="40" t="s">
         <v>46</v>
       </c>
